--- a/output/2026-09-02_19_Italia_Molise_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-02_19_Italia_Molise_Componentistica_Ventilazione_industriale.xlsx
@@ -494,10 +494,9 @@
           <t>0874 62009</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Forniture industriali B2B storiche (dal 1990); catalogo confermato include aria compressa/vuototecnica e macchine/accessori per pulizia industriale</t>
+          <t>Forniture industriali B2B storiche (dal 1990); catalogo confermato include aria compressa/vuototecnica e macchine/accessori per pulizia industriale [DUPLICATO — vedi anche: 2026-09-02_16_Italia_Molise_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -532,10 +531,9 @@
           <t>0875 707360</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Forniture industriali B2B a Termoli; fonti confermano esplicitamente vendita di aspiratori industriali, pneumatica, compressori</t>
+          <t>Forniture industriali B2B a Termoli; fonti confermano esplicitamente vendita di aspiratori industriali, pneumatica, compressori [DUPLICATO — vedi anche: 2026-09-02_18_Italia_Molise_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
